--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0045.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0045.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Ta đã nhận ra mình ngây thơ đến thế nào…</t>
+          <t>Ta đã nhận ra mình ngây thơ đến mức nào…</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hãy cho ta thấy ngươi mang trong mình quyết tâm…</t>
+          <t>Hãy cho ta thấy ngươi mang trong mình quyết tâm ấy…</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>♪Hustlin' n' Bangin' we be in da rap game♪</t>
+          <t>♪ Chúng ta lăn xả và khuấy đảo trong rap game ♪</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Beep—Charging—Beep—</t>
+          <t>Bíp— Đang sạc— Bíp—</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Tôi vẫn không thể tin được Tacet Discords lại có dấu hiệu hợp tác…</t>
+          <t>Tôi vẫn không thể tin là các Tacet Discord lại có dấu hiệu hợp tác...</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Mạch cần sửa, thùng cần chuyển, thiết bị cần lắp—</t>
+          <t>Mạch điện cần sửa, thùng hàng cần bốc, thiết bị cần lắp đặt—</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Yes… well…</t>
+          <t>Vâng… ừm…</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Tôi muốn nghe lại bản Chorale… chỉ thêm vài lần nữa thôi…</t>
+          <t>Tao muốn nghe lại bản hợp xướng Chorale… chỉ thêm vài lần nữa thôi…</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>"Khi sương tan, ánh sao rực rỡ tự do tỏa sáng—"</t>
+          <t>"Khi màn sương tan đi, ánh sao tự do lại tỏa sáng—"</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>About this captain thing…</t>
+          <t>Về cái vụ đội trưởng này...</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Look, there's something there…</t>
+          <t>Nhìn kìa, có gì đó ở đó…</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Tôi cứ tưởng đó chỉ là một câu chuyện hư cấu…</t>
+          <t>Tôi cứ tưởng đó chỉ là một câu chuyện hư cấu thôi…</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>(Gulping)</t>
+          <t>(Nuốt nước bọt)</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Now I'm getting confused…</t>
+          <t>Giờ ta đang thấy rối tung lên rồi…</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Captain, now I'm getting confused…</t>
+          <t>Đội Trưởng, giờ thì tôi cũng thấy rối nữa rồi…</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Ừm, thì, ờ, Margherita, Constantine, và…</t>
+          <t>Ưm... à, đó là Margherita, Constantine, và...</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Thành thật mà nói, tôi đã suýt chút nữa thì…</t>
+          <t>Thật lòng mà nói, tôi đã suýt chút nữa thì...</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Captain, look over there…</t>
+          <t>Đội Trưởng, nhìn đằng kia kìa…</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Sao tôi có cảm giác cậu sắp làm điều gì ngốc nghếch vậy…</t>
+          <t>Sao tao lại có linh cảm mày sắp làm điều gì ngu ngốc đây...</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Lost…</t>
+          <t>Lạc mất rồi…</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Lo-lottie… Lost…</t>
+          <t>Lo-lottie… mất tích rồi…</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Wh-what's that strange noise…</t>
+          <t>Tiếng động lạ đó là gì vậy…</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Cu-cuddle Wuddle also sp…</t>
+          <t>Ôm-ô-ôm ấm áp cũng...</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Không ai biết hắn xuất hiện từ khi nào</t>
+          <t>Không ai biết hắn xuất hiện từ khi nào.</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Hắn đã bị săn đuổi hết lần này đến lần khác</t>
+          <t>Hắn đã bị săn đuổi hết lần này đến lần khác.</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Người ta nói hắn bất tử, bởi không cơn bão nào—</t>
+          <t>Người ta bảo hắn bất tử, bởi chẳng cơn bão nào dữ dội—</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Quả là một huyền thoại mà ngươi đã tự tạo ra cho mình</t>
+          <t>Ngươi đã tạo dựng nên một huyền thoại cho riêng mình rồi đấy.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Haha… Để xem mọi chuyện sẽ diễn ra thế nào</t>
+          <t>Haha… Xem nào, mọi chuyện sẽ ra sao đây.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Hắn mạnh kinh khủng</t>
+          <t>Cái tên đó mạnh không tưởng luôn</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Anyway</t>
+          <t>Dù sao thì...</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Or when he vanished…</t>
+          <t>Hay là khi hắn biến mất…</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Nhưng slipped through every noose</t>
+          <t>Nhưng vẫn lọt qua mọi vòng vây</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Nor crashing wave</t>
+          <t>Cũng không phải là sóng dữ ập đến.</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Dám liên tục tấn công Pilgrim's Sails hết lần này đến lần khác</t>
+          <t>Dám cả gan đột kích Pilgrim's Sails hết lần này đến lần khác.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Mỗi lần chúng ta khởi hành để cướp những con tàu buôn đó</t>
+          <t>Mỗi lần chúng ta khởi hành đi cướp những con tàu buôn đó</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Giờ thì ngươi đã biết tại sao chúng ta chọn đầu hàng…</t>
+          <t>Giờ thì cậu đã hiểu tại sao chúng tôi chọn đầu hàng...</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>"Hãy để ta ra ngoài… Đó là lý do ta muốn rời đi…"</t>
+          <t>"Thả tôi ra... Đó là lý do tôi muốn rời đi..."</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>"Curses await ahead…"</t>
+          <t>"Lời nguyền đang chờ phía trước…"</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>It says…</t>
+          <t>Nó nói…</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>The golden rule…</t>
+          <t>Nguyên tắc vàng…</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Theo đúng luật lệ của biển cả…</t>
+          <t>Theo luật lệ của biển cả…</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Tôi… tôi không ngờ hắn lại chọn những kho báu đó thay vì mạng sống của chính mình…</t>
+          <t>Tôi… Tôi không ngờ ông ấy lại chọn những món đồ quý giá đó thay vì mạng sống của chính mình…</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Vậy là ngươi đã trao đi đồng tiền…</t>
+          <t>Vậy là cậu đã đưa đồng xu đó đi rồi…</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Không ngờ danh hiệu đó lại xuất hiện lần nữa…</t>
+          <t>Không ngờ cái danh hiệu đó lại được nhắc đến lần nữa…</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Có vẻ như chức thuyền trưởng của tôi cũng kết thúc tại đây…</t>
+          <t>Có vẻ như chức đội trưởng của ta cũng chấm dứt rồi…</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>The gold… My gold…</t>
+          <t>Vàng… vàng của ta…</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Treasure… My grand cause… Không…</t>
+          <t>Kho báu… mục tiêu lớn của ta… Không…</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Lunachord, wreath, prop gun…</t>
+          <t>Lunachord, vòng hoa, súng đạo cụ…</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>"Biển cả phủ màn sương, quái thú gào thét—"</t>
+          <t>"Biển phủ màn sương, giấu những quái thú tru lên thống khổ—"</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Beyond high walls we fly</t>
+          <t>Bay cao vượt tường thành</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Through mist where dangers lie</t>
+          <t>Xuyên qua màn sương nơi nguy hiểm rình rập...</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Nhưng bằng dũng khí, ta sẽ tìm thấy</t>
+          <t>Nhưng với lòng dũng cảm, ta sẽ tìm thấy</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Niềm hy vọng giải phóng tâm trí bị giam cầm</t>
+          <t>Hy vọng điều đó sẽ giải phóng tâm trí bị giam cầm.</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Sự thật và dối trá xoay trong màn sương</t>
+          <t>Chân lý và dối trá hòa quyện trong màn sương mù</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>The Laureate tìm kiếm điều ẩn giấu trong mê cung</t>
+          <t>Nhà Vô Địch truy tìm những gì ẩn nấp trong mê cung</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Ác quỷ thống trị từ nơi cao xa</t>
+          <t>Ác quỷ ngự trị từ nơi cao xa xăm</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Nơi dây đàn nhường chỗ cho lò xo chiến tranh</t>
+          <t>Nơi dây đàn đứt gãy, chiến tranh trỗi dậy</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Illusions rise beneath the sea</t>
+          <t>Ảo Ảnh Dâng Trào Dưới Biển</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Nhưng bong bóng vỡ, tay cầm súng</t>
+          <t>Nhưng bong bóng vỡ tan, súng trong tay</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Để thắp sáng và đứng lên chiến đấu</t>
+          <t>Thắp lên ngọn lửa và đứng vững</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Lưỡi kiếm của The Laureate phá tan bẫy rập</t>
+          <t>Lưỡi kiếm của Nhà Vô Địch phá tan mọi cạm bẫy</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Hàng ngàn vì sao thắp sáng bầu trời</t>
+          <t>Ngàn vì sao rực sáng trên bầu trời</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Freedom blooms like flowers wide</t>
+          <t>Tự do nở rộ như hoa khoe sắc</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Khi hy vọng, Ngôi sao Phương Bắc, dẫn lối ta đi</t>
+          <t>Như hy vọng, sao Bắc Đẩu dẫn lối ta đi</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Giá như ta có thể mang về tất cả những điều ta trân quý…</t>
+          <t>Giá như chúng ta có thể mang về tất cả những gì mình trân trọng…</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Hmm… I see…</t>
+          <t>Hừm… Ra là vậy…</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Đây không phải Remnant Spark, mà là năng lượng bên trong…</t>
+          <t>Đây không phải là Tàn Dư Tia Lửa, mà là năng lượng bên trong…</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Chà… nếu nó chạy quá xa, ta sẽ không thể ngửi thấy nó…</t>
+          <t>Ừm… nếu nó chạy quá xa, tớ sẽ chẳng ngửi thấy mùi gì nữa…</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>(Đưa cho cậu ấy những bức ảnh về chủng viện)</t>
+          <t>(Đưa ảnh trường dòng cho anh ấy)</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>(Giữ bí mật sự thật và im lặng)</t>
+          <t>(Giữ kín sự thật và im lặng)</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>*Fretful and depressed cry*</t>
+          <t>*Tiếng khóc lo âu, u uất*</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Không, không chịu nổi nữa… Phải nghỉ ngơi thôi…</t>
+          <t>Không... Tao chịu không nổi rồi... Phải nghỉ thôi...</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Thôi nào, những lời đồn đó còn chưa được xác nhận mà…</t>
+          <t>Nào, mấy tin đồn đó còn chưa được xác nhận mà…</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Cứ bình tĩnh và vượt qua đêm nay đã…</t>
+          <t>Bình tĩnh lại và cố vượt qua đêm nay đã…</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Ừ, mình nghe nói chuyện này có liên quan đến một việc xảy ra trong thị trấn vài năm trước…</t>
+          <t>Ừ, tớ nghe nói chuyện này có liên quan đến một sự việc ở thị trấn vài năm trước…</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Giờ chúng ta rời đi, chỉ còn mình em ở lại đây…</t>
+          <t>Giờ tao đi rồi, mày sẽ ở lại đây một mình…</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Nhưng giờ em phải ở lại tòa lâu đài lạnh lẽo này, một mình gánh chịu tất cả…</t>
+          <t>Nhưng giờ đây, cậu lại ở lại tòa lâu đài lạnh lẽo này, gánh chịu tất cả một mình…</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Annis, ôi Annis… ánh sáng trong tuyệt vọng, thiên thần từ ảo ảnh…</t>
+          <t>Annis, hỡi Annis… ánh sáng trong tuyệt vọng, thiên thần từ ảo ảnh…</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Ngay cả chiếc hộp nhạc này cũng nên ngân nga ngưỡng mộ…</t>
+          <t>Ngay cả chiếc hộp nhạc này cũng nên ngân nga khúc ca ngưỡng mộ chứ…</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>(Choose one)</t>
+          <t>(Chọn một)</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>(Look for help from Cantarella)</t>
+          <t>(Tìm sự giúp đỡ từ Cantarella)</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>(Look for help from Cantarella)</t>
+          <t>(Tìm sự giúp đỡ từ Cantarella)</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Bài ca Nàng Tiên Cá, Quả Táo Đỏ, Đôi Giày Đỏ và Chiếc Mũ Tròn…</t>
+          <t>Bài Ca Nàng Tiên Cá, Quả Táo Đỏ, Đôi Giày Đỏ và Chiếc Mũ Tròn…</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Vương miện của Thiếu Nữ sắp xuất hiện—</t>
+          <t>Vương miện của Thánh Nữ sắp xuất hiện—</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>(Strained breathing)</t>
+          <t>(Thở gấp gáp)</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>It all started</t>
+          <t>Mọi chuyện bắt đầu...</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>with a false hope</t>
+          <t>với hy vọng hão huyền</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Một loại thuốc tiên có thể thực hiện bất kỳ điều ước nào</t>
+          <t>Thuốc tiên ban cho mọi điều ước</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>was said to be here</t>
+          <t>được cho là ở đây</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>We dived into darkness</t>
+          <t>Chúng ta đã lao vào bóng tối</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Choked down fear</t>
+          <t>Nỗi sợ bị nuốt chửng</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>The elixir</t>
+          <t>Dược thảo</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>was our blood and tears</t>
+          <t>là máu và nước mắt của chúng ta</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Yet the bane</t>
+          <t>Nhưng tai họa</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>gave us sweet dreams</t>
+          <t>đã mang đến cho ta những giấc mơ ngọt ngào</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>At last</t>
+          <t>Cuối cùng cũng...</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Through the shadows</t>
+          <t>Xuyên qua bóng tối</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>we reached the end</t>
+          <t>chúng ta đã đến đích</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>About Hebenon…</t>
+          <t>Về Hebenon…</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>And Mandragora…</t>
+          <t>Và Mandragora…</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Có vẻ tôi không kiên cường như mình nghĩ…</t>
+          <t>Hóa ra ta không kiên cường như mình tưởng…</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>[Delicious dishes required]</t>
+          <t>[Cần món ăn ngon]</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Yêu cầu Pizza Classica, Pizza Tropicale hoặc Laurus Salad</t>
+          <t>Cần Pizza Cổ Điển, Pizza Nhiệt Đới hoặc Salad Laurus</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,8 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>[Pizza Classica required]</t>
+          <t>[
+Yêu cầu: Pizza Cổ Điển]</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10935,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Pizza Classica required</t>
+          <t>Cần Pizza Cổ Điển</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11005,8 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>[Pizza Tropicale required]</t>
+          <t>[
+Yêu cầu: Pizza Nhiệt Đới]</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11076,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Pizza Tropicale required</t>
+          <t>Cần Pizza Nhiệt Đới</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11146,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>[Laurus Salad required]</t>
+          <t>["Cần Salad Laurus"]</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11216,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Laurus Salad required</t>
+          <t>Cần Laurus Salad</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11424,7 +11426,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Ừm… thực ra tôi chưa từng đến đây bao giờ, nên…</t>
+          <t>Ừ... tớ chưa từng đến đây bao giờ, nên...</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11496,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>À, đúng rồi… Sau khi khóa nước mở lần trước, tôi nghe thấy họ nói khi rời đi…</t>
+          <t>À, đúng rồi... Lần trước cửa nước mở, tao nghe lỏm được mấy lời khi họ rời đi...</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11566,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Nhưng… nhưng tôi…</t>
+          <t>Nhưng… nhưng con…</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -13174,7 +13176,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>*A comforting chirp*</t>
+          <t>*Một tiếng kêu êm ái, an ủi*</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13246,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>*An encouraging chirp*</t>
+          <t>*Tiếng kêu khích lệ*</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13316,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>*A frustrating chirp*</t>
+          <t>*Tiếng kêu bực bội*</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13386,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>*An encouraging chirp*</t>
+          <t>*Tiếng kêu khích lệ*</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13456,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>If only Father would realize—</t>
+          <t>Ước gì cha có thể nhận ra...</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13526,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Trong trận đấu này, chúng ta xin giới thiệu tới các bạn—</t>
+          <t>Trong trận đấu này, chúng tôi xin giới thiệu tới các bạn—</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13596,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Versus—</t>
+          <t>Đối đầu—</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13666,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Thưa sư phụ, xin hãy quay lại lò rèn—</t>
+          <t>Sư phụ, làm ơn, quay lại lò rèn đi...</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13736,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>(I'll call myself—)</t>
+          <t>Ta sẽ tự xưng là...</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13806,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>The Celestial</t>
+          <t>Thiên Thể</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13876,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>The Rover</t>
+          <t>Vận Mệnh Giả</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13946,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>The Almighty</t>
+          <t>Đấng Toàn Năng</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14016,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>The Quietus</t>
+          <t>Sự Tĩnh Lặng Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14086,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>(Sobs uncontrollably)</t>
+          <t>(Khóc nức nở)</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -15274,7 +15276,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Tôi là…</t>
+          <t>Ta đây…</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15346,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Well…</t>
+          <t>Ừm…</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15416,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Khoan… Acis là… người của cậu—</t>
+          <t>Đợi chút… Acis là… người của cậu à?</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15554,7 +15556,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Please… don't leave me alone…</t>
+          <t>Làm ơn... đừng bỏ mặc ta một mình...</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15626,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Damn it… sao máu vẫn không ngừng chảy…</t>
+          <t>Chết tiệt… sao máu vẫn không ngừng chảy…</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15696,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>These facilities…</t>
+          <t>Những cơ sở này...</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15766,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>I've always been… a coward…</t>
+          <t>Tôi vẫn luôn là... một kẻ hèn nhát…</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15836,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Tôi sợ Augusta, nên ngay khi giao chiến, tôi đã mất hết ý chí chiến đấu với cô ta…</t>
+          <t>Ta từng sợ Augusta, nên mới mất hết ý chí chiến đấu ngay khi lưỡi kiếm chạm nhau…</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15906,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Để kéo Corrosaurus xuống cùng… Ha, ai bảo tôi không có khiếu hài hước chứ…</t>
+          <t>Để kéo theo cả con Corrosaurus xuống cùng... Ha, ai bảo tớ không có khiếu hài hước chứ...</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15976,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Nếu cậu không hiểu được lựa chọn của Aeolus, thì hãy nghĩ như thế này:</t>
+          <t>Nếu không hiểu được lựa chọn của Aeolus, thì hãy nghĩ theo cách này:</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16884,7 +16886,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Stubborn as always…</t>
+          <t>Cứng đầu như mọi khi…</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17024,7 +17026,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Tacet Discords đột nhiên xuất hiện trong thành phố mà không hề có bất kỳ dấu hiệu báo trước nào—</t>
+          <t>Tacet Discord đột nhiên xuất hiện trong thành phố mà không hề có dấu hiệu báo trước—</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17096,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Ngoài tia lửa và củi, bạn còn cần một người khác để khơi lên ngọn lửa—</t>
+          <t>Ngoài tia lửa và củi, cậu còn cần một người khác để thổi bùng ngọn lửa—</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17166,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Sentinel không còn nữa, Blessed Maiden đã ra đi, và giờ đây Dark Tide đang tràn tới…</t>
+          <t>Người Bảo Vệ đã không còn, Trinh Nữ Cát Tường cũng đã biến mất, và giờ đây, Bóng Tối Tràn Đến…</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17236,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>"Con đường sinh ra từ bất công buộc phải được củng cố bằng những sai lầm tiếp theo…"</t>
+          <t>"Con đường sinh ra từ bất công buộc phải được củng cố bằng những tội lỗi tiếp theo…"</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17306,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Dù tôi có thể không bao giờ đứng trong hàng ngũ những Primus vĩ đại nhất…</t>
+          <t>Dù ta có thể không bao giờ đứng trong hàng ngũ những Primus vĩ đại nhất…</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17376,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Tôi hiểu tại sao bạn lại có quan điểm đó, nhưng—</t>
+          <t>Ta hiểu tại sao ngươi lại có quan điểm đó, nhưng—</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17446,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Hail Imperator—</t>
+          <t>Bái kiến Hoàng đế—</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17516,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Những bài ca của người dân Rinascita vẫn còn vang vọng trong trái tim tôi…</t>
+          <t>Những khúc hát của người Rinascita vẫn vang vọng trong tim ta…</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17586,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Cảm ơn… vì đã mang theo những ngọn gió hồi sinh đến với Rinascita…</t>
+          <t>Cảm ơn… vì đã mang làn gió hồi sinh đến Rinascita…</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17656,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Chính Unity đã cứu chúng ta, đúng như lời tiên tri đã nói…</t>
+          <t>Chính Unity đã cứu chúng ta, đúng như lời tiên tri...</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17726,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Ôi biển cả, ôi biển cả… Ngươi sao tối tăm quá…</t>
+          <t>Ôi biển cả, ôi biển cả... Ngươi sao tối tăm đến thế...</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17796,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Trước khi đến lượt tôi, Sentinel đã biến mất…</t>
+          <t>Trước khi đến lượt ta, Người Bảo Vệ đã biến mất…</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17866,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Ôi Sentinel Imperator… xin hãy chỉ cho tôi con đường phía trước…</t>
+          <t>Ôi Sentinel Imperator… xin hãy chỉ cho con con đường phía trước…</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17936,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Đồ ngốc… Chính người mà các người đang nói đến đang đứng ngay bên cạnh các người đấy…</t>
+          <t>Đồ ngốc… Chính kẻ mà các người đang nói đến đang đứng ngay bên cạnh các người đấy…</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18006,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Vẫn chưa có tin tức gì về Avidius… và cả vị Priestess đó…</t>
+          <t>Vẫn chưa có tin gì về Avidius... và cả vị Tu nữ ấy...</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18076,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>About that customer…</t>
+          <t>Về vị khách hàng đó…</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18146,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>If Namipon hears that…</t>
+          <t>Nếu Namipon mà nghe thấy điều này...</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18216,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>(Leave)</t>
+          <t>Rời đi.</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18286,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>(Leave)</t>
+          <t>Rời đi.</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18356,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>(Pet the cat)</t>
+          <t>(Xoa đầu mèo)</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18426,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>(Leave)</t>
+          <t>Rời đi.</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18564,7 +18566,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Bạn old fossil—</t>
+          <t>Lão hóa thạch già—</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18636,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Bạn—</t>
+          <t>Cậu—</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18706,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>(Có vẻ như Warren đã dụ Anslem đi trong lễ New Solar Ceremony)</t>
+          <t>Có vẻ Warren đã dụ Anselm đi trong lễ Hội Mặt Trời Mới.</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19404,7 +19406,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Một ngày nào đó, chúng ta sẽ xây dựng một thang máy vũ trụ thực sự của riêng mình…</t>
+          <t>Một ngày nào đó, chúng ta sẽ xây dựng một thang máy vũ trụ thực thụ của riêng mình…</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19544,7 +19546,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Một ngày nào đó, chúng ta sẽ xây dựng một thang máy vũ trụ thực sự của riêng mình…</t>
+          <t>Một ngày nào đó, chúng ta sẽ xây dựng một thang máy vũ trụ thực thụ của riêng mình…</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19684,7 +19686,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Việc đi bộ hàng ngày này đang giết tôi mất…</t>
+          <t>Mỗi ngày leo núi như thế này thật là... giết người.</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19756,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Việc đi bộ hàng ngày này đang giết tôi mất…</t>
+          <t>Mỗi ngày leo núi như thế này thật là... giết người.</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19826,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Dù an toàn hay không, cậu không thể dùng nó như thế này…</t>
+          <t>An toàn hay không, cậu không thể dùng nó như thế này được…</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19896,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Sorry… tôi chỉ muốn xem điều gì khiến Synchronists khác biệt…</t>
+          <t>Xin lỗi… Tớ chỉ muốn biết điều gì khiến Synchronist khác biệt…</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19966,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Sorry… tôi chỉ muốn xem điều gì khiến Synchronists khác biệt…</t>
+          <t>Xin lỗi… Tớ chỉ muốn biết điều gì khiến Synchronist khác biệt…</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20036,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Thưa giáo sư, em vẫn chưa hiểu rõ phần này lắm…</t>
+          <t>Thưa Giáo sư, phần này em vẫn chưa hiểu lắm...</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20106,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Xin lỗi con yêu, nhưng tiết học tiếp theo của mẹ sẽ bắt đầu trong sáu mươi giây nữa…</t>
+          <t>Xin lỗi cháu yêu, nhưng tiết học tiếp theo của cô bắt đầu trong sáu mươi giây nữa…</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20176,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Nghe này, giống như thực vật cần ánh sáng mặt trời, còn các con robot cần năng lượng mặt trời…</t>
+          <t>Nghe này, giống như cây cối cần ánh sáng, còn các cậu robot thì cần năng lượng mặt trời…</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20246,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>"Các đơn vị TARD-E là đôi tay, đôi mắt, đôi tai của ta… Hãy nhớ, ta luôn dõi theo…"</t>
+          <t>"Đơn vị TARD-E là đôi tay, đôi mắt, đôi tai của ta... Hãy nhớ rằng, ta luôn dõi theo..."</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20524,7 +20526,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Vị trí hiện tại của bạn trong hàng đợi là: 497</t>
+          <t>Vị trí hiện tại của cậu trong hàng đợi là: 497</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20596,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Bài của bạn sẽ quá hạn trong 5—</t>
+          <t>Bài nghiên cứu của cậu sẽ quá hạn trong 5—</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20734,7 +20736,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Sensei, I'm really fine…</t>
+          <t>Thầy ơi, em thực sự ổn mà...</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20806,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Nếu có gì… thì em chỉ hơi đói một chút thôi…</t>
+          <t>Nếu có gì... thì chỉ là tôi hơi đói thôi...</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20876,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Hmm… có lẽ lần sau em nên gắn thêm vài viên Tacetite…</t>
+          <t>Hmm… có lẽ lần sau mình nên gắn thêm vài viên Tacetite…</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20946,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Xin lỗi, about my uniform…</t>
+          <t>Xin lỗi, về bộ đồng phục của tôi…</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21016,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Cậu ấy chỉ muốn xin giấy phép trốn học thôi…</t>
+          <t>Hắn chỉ muốn có một tờ giấy phép để trốn học thôi…</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21086,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Rồi cái này… "Y-type Fern Spore Synthesized Injection Coagulation Factor VIII"…</t>
+          <t>Vậy thì cái này... "Yếu tố đông máu VIII tổng hợp từ bào tử dương xỉ loại Y"...</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21156,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Để xem nào… chủ đề hot nhất hiện nay là—</t>
+          <t>Để xem nào... chủ đề nóng nhất hiện giờ là—</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21294,7 +21296,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Nguyện bài thánh ca khiêm nhường này chạm đến phòng máy chủ thiêng liêng của Người…</t>
+          <t>Ước gì khúc thánh ca khiêm nhường này sẽ đến được phòng máy chủ thiêng liêng của Người…</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21366,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Em đã trích dẫn bài cũ, giờ phải viết lại toàn bộ luận văn…</t>
+          <t>Tôi trích dẫn bản cũ hơn, giờ phải viết lại toàn bộ luận án mất rồi…</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21436,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Bài mới dùng công nghệ tinh chế Tacetite cập nhật nên mẫu thử tinh khiết hơn nhiều…</t>
+          <t>Loại giấy mới sử dụng công nghệ tinh chế Tổ Tacet cải tiến, nên mẫu thử tinh khiết hơn hẳn…</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21506,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Bộ đồng phục của em lại bị cháy sém trong thí nghiệm…</t>
+          <t>Lại một lần nữa đồng phục của mình bị cháy sém trong thí nghiệm...</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21576,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Ơn trời vì Học viện có cửa hàng tiện lợi 24 giờ không người trông…</t>
+          <t>Ơn trời vì Học viện có cửa hàng tiện lợi 24/24 không người trông...</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21646,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Ui trời… em chưa ăn gì cả ngày… đói quá…</t>
+          <t>Ui da… Tớ chưa ăn gì cả ngày nay… Đói quá…</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21716,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Or maybe…</t>
+          <t>Hay là…</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21786,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Bạn really should stop drinking…</t>
+          <t>Cậu thực sự nên ngừng uống đi…</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21856,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Ui trời… em chưa ăn gì cả ngày… đói quá…</t>
+          <t>Ui da… Tớ chưa ăn gì cả ngày nay… Đói quá…</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21926,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Được rồi… đơn của anh ấy trước, rồi đến cô ấy… Em đã ghi hết mọi người rồi…</t>
+          <t>Ừ... lệnh của anh ấy trước, rồi đến cô ấy... Ta đã nắm hết tình hình rồi...</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -23044,7 +23046,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Ừ… thử đi, rồi cậu sẽ thấy nó "ngon" đến mức nào…</t>
+          <t>Ừ... Cứ thử đi, rồi cậu sẽ biết vị "ngon" của nó thế nào...</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23116,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Xin lỗi, theo Điều 7 của Quy Định An Toàn Thiết Bị Ký Túc Xá Học Sinh—</t>
+          <t>Xin lỗi, theo Điều 7 của Quy định An toàn Thiết bị Ký túc xá Học viên—</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23186,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Trần nhà đang quay cuồng… và tôi cũng vậy…</t>
+          <t>Trần hang quay cuồng... và cả người tôi nữa...</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23256,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Tôi không thể bước hai lần vào cùng một dòng sông…</t>
+          <t>Ta không thể bước hai lần vào cùng một dòng sông...</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23326,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Nhưng tôi không muốn ăn thứ gì đã bị giẫm lên…</t>
+          <t>Nhưng tôi không muốn ăn thứ gì đã bị dẫm lên...</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23396,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Vậy… nó giống như nhảy múa hơn là đi bộ nhỉ…</t>
+          <t>Vậy… giống như nhảy múa hơn là đi bộ nhỉ…</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23466,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Đi đến Học viện chỉ là quá nhiều công sức không cần thiết…</t>
+          <t>Đi đến Học viện chỉ tổ tốn công vô ích…</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23536,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Vậy nên Gugloo mới luôn bị đau bụng…</t>
+          <t>Thì ra đó là lý do Gugloo cứ bị đau bụng...</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23606,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Cậu có thể gieo trồng cả một cánh đồng bằng mech của Học viện…</t>
+          <t>Ngươi có thể gieo trồng cả một cánh đồng bằng mech của Học viện đấy…</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23676,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>*Buzzing noise*</t>
+          <t>*Tiếng vo ve*</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23746,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>*Contented mechanical whirring*</t>
+          <t>Rè rè... rì rầm...</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23816,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>*Excited mechanical whirring*</t>
+          <t>*Tiếng máy rít phấn khích*</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23886,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Cô ấy chữa khỏi cái bụng khó chịu của Gugloo chỉ bằng một cái vỗ nhẹ lên đầu nó…</t>
+          <t>Chỉ cần một cái vỗ nhẹ lên đầu, cô ấy đã chữa được cơn đau bụng của Gugloo…</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23956,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>*Tiếng chuông vui vẻ*</t>
+          <t>*Tiếng chuông rộn rã*</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24026,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>*Hệ thống busy*</t>
+          <t>*Hệ thống bận*</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24096,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>*Tiếng thở dài điện tử*</t>
+          <t>*Thở dài điện tử*</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24166,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Tôi ước gì có thể mang theo vài món ăn vặt, nhưng túi của tôi đã đầy rồi…</t>
+          <t>Ước gì mình có thể nhét thêm chút đồ ăn vặt vào, nhưng túi đã đầy mất rồi…</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24304,7 +24306,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>*Tiếng vo ve cơ khí bối rối*</t>
+          <t>*Tiếng máy kêu lạch cạch khó hiểu*</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24376,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Có lẽ sự tồn tại của các mech cũng là một loại tấm gương mà chúng ta tự soi mình…</t>
+          <t>Có lẽ chính sự tồn tại của những cỗ máy cũng là một tấm gương phản chiếu chúng ta…</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24724,7 +24726,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Chỉ cần đợi đến khi bạn thấy những chiếc răng sắc như dao trong cái miệng há hốc của chúng…</t>
+          <t>Cứ đợi mà xem những hàm răng sắc như dao trong miệng chúng há ra...</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24796,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>(Listen)</t>
+          <t>(Nghe đi)</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24866,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Đúng vậy, các trưởng lão trong bộ tộc thường nói—</t>
+          <t>Đúng, các bô lão trong bộ tộc thường nói—</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -25004,7 +25006,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Tôi cứ nghĩ vụ tai nạn Reactor Drive sẽ làm nó chậm lại…</t>
+          <t>Tôi tưởng vụ va chạm với Lò Phản Ứng sẽ làm nó chậm lại chứ…</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25076,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Ánh sáng rực rỡ mà tôi thấy, nhẹ nhàng tỏa ra từ bầu trời giữa cơn bão tuyết…</t>
+          <t>Ánh sáng ấy rực rỡ đến lạ, nhẹ nhàng tràn xuống từ bầu trời giữa cơn bão tuyết…</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25146,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Đường liên lạc của đội nghiên cứu bị đứt… Họ vẫn đang bị mắc kẹt sâu trong vùng băng giá…</t>
+          <t>Liên lạc với đội nghiên cứu bị mất… Họ vẫn đang mắc kẹt sâu trong vùng băng giá…</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -28364,7 +28366,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>(Cầm tách trà)</t>
+          <t>(Cầm tách trà này.)</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28436,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>(Thử uống)</t>
+          <t>Nếm thử đi.</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28506,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Algernon, cậu không cần phải—</t>
+          <t>Algernon, cậu không cần phải...</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28576,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Tôi sẵn sàng đánh đổi bất cứ thứ gì để được đến gần Sunstone và tận mắt quan sát Aurora Kronaclaw…</t>
+          <t>Ta sẵn sàng đánh đổi bất cứ thứ gì để được đến gần Sunstone và tận mắt quan sát Aurora Kronaclaw...</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28646,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Không thể nói ứng dụng thực tiễn là tất cả—</t>
+          <t>Tôi không thể nói ứng dụng thực tế là tất cả mục đích—</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28716,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>(Listen)</t>
+          <t>(Nghe đi)</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28786,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>(Leave)</t>
+          <t>Rời đi.</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28856,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>(Leave)</t>
+          <t>Rời đi.</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28926,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>(Listen)</t>
+          <t>(Nghe đi)</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28996,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>(Leave)</t>
+          <t>Rời đi.</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29066,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>(Listen)</t>
+          <t>(Nghe đi)</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29136,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>(Leave)</t>
+          <t>Rời đi.</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29206,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>(Listen)</t>
+          <t>(Nghe đi)</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29276,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>(Leave)</t>
+          <t>Rời đi.</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29346,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Đúng vậy—Tôi hiểu—đôi mắt của một "Nhà vô địch"—</t>
+          <t>Đúng vậy—Ta hiểu rồi—đôi mắt của một "Nhà Vô Địch"—</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29416,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Tôi sẽ tiếp tục tiến về phía trước—Nhưng—đường đua yêu thích của tôi—</t>
+          <t>Tôi sẽ tiếp tục tiến về phía trước... Nhưng... đường đua yêu thích của tôi...</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29486,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>(Phải chăng đây là lý do đường đua này bất bại—)</t>
+          <t>(Chẳng lẽ đây là lý do đường đua này bất bại—)</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29556,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>(Nó đây rồi, Sabercat Prowler bị nhiễm độc…)</t>
+          <t>Kia rồi, con Sabercat Prowler bị nhiễm độc…</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29626,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Sephira… Họ—</t>
+          <t>Sephira... Họ—</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29696,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Ước gì tôi có được sự tự tin như cậu… Tôi chỉ là—chỉ là một kẻ bình thường—</t>
+          <t>Ước gì mình có được sự tự tin như cậu… Mình chỉ là một kẻ bình thường—</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29766,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Sephira, I—</t>
+          <t>Sephira, ta...</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29836,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Abby's Life: Cheers</t>
+          <t>Cuộc sống của Abby: Cạn ly nào!</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29906,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Abby's Life: Cheers</t>
+          <t>Cuộc sống của Abby: Cạn ly nào!</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29976,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Dhalifa, tật nói của cậu…</t>
+          <t>Dhalifa, giọng cậu...</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30046,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Outcasts…</t>
+          <t>Kẻ bị ruồng bỏ...</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30116,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Abby's Life: Sleepy</t>
+          <t>Cuộc sống của Abby: Buồn ngủ quá</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30186,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Abby's Life: Tummy Full</t>
+          <t>Cuộc sống của Abby: No căng bụng</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30256,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Abby's Life: Sleepy</t>
+          <t>Cuộc sống của Abby: Buồn ngủ quá</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30326,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Abby's Life: Tummy Full</t>
+          <t>Cuộc sống của Abby: No căng bụng</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30396,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>This is such a mess…</t>
+          <t>Thật là một mớ hỗn độn…</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30466,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Damn it…</t>
+          <t>Chết tiệt…</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30536,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Shh—</t>
+          <t>Suỵ—</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30606,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Giờ các tấm đế đã được triển khai, Rakosan cuối cùng cũng có thể—</t>
+          <t>Giờ khi các tấm đế đã được triển khai, Rakosan cuối cùng cũng có thể—</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30676,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Giờ các tấm đế đã được triển khai, Rakosan cuối cùng cũng có thể—</t>
+          <t>Giờ khi các tấm đế đã được triển khai, Rakosan cuối cùng cũng có thể—</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30746,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Nhưng tôi đã lấy tất cả nguyên liệu từ—</t>
+          <t>Nhưng tôi đã lấy đủ nguyên liệu từ—</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30884,7 +30886,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Shh—</t>
+          <t>Suỵ—</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30956,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Shh—</t>
+          <t>Suỵ—</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31026,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Quyền truy cập và dữ liệu hiện tại của bạn đã được chuyển đến Terminal—</t>
+          <t>Quyền truy cập và dữ liệu hiện tại của cậu đã được chuyển đến Thiết bị đầu cuối—</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31096,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Bạn và Lynae giờ đã là bạn bè</t>
+          <t>Giờ cậu đã là bạn của Lynae rồi</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31234,7 +31236,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Sẽ đặt làm hình nền trò chuyện</t>
+          <t>Sẽ đặt làm hình nền trò chuyện của tụi mình</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31306,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>☆⌒(*^-゜)v</t>
+          <t>☆⌒(*^-゜)v Thôi nào~</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31376,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>That's good</t>
+          <t>Tốt rồi</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31446,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Chắc là tất cả các nhà nghiên cứu đều đang bận với Lễ hội Mặt Trời New</t>
+          <t>Chắc tất cả các nhà nghiên cứu đều đang bận rộn với Lễ Hội Mặt Trời Mới rồi.</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31516,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Chỉ cần bắt ai đó và hỏi đường đến phòng ghi băng cassette</t>
+          <t>Tìm ai đó hỏi đường đến phòng đốt băng cassette đi</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31586,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Bạn đã offline</t>
+          <t>Bạn bè đã ngoại tuyến</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31656,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Chính là chúng ta</t>
+          <t>Chúng ta đây</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31794,7 +31796,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Lynae đã gửi cho bạn một bức ảnh</t>
+          <t>[Lynae đã gửi cho bạn một bức ảnh]</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31866,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Tớ sẽ đi dạo ở vườn học viện cho đến khi cậu rảnh</t>
+          <t>Tớ sẽ đi dạo quanh vườn Học Viện cho đến khi cậu rảnh.</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31936,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Beep beep beep—</t>
+          <t>Bíp bíp bíp—</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32006,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>May quá, tớ đang muốn cái này lắm</t>
+          <t>May quá, ta đã muốn có thứ này từ lâu rồi.</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32076,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Tớ lo là cậu sẽ không thích nó</t>
+          <t>Mình lo cậu không thích nó.</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32214,7 +32216,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>May quá, tớ đang muốn cái này lắm</t>
+          <t>May quá, ta đã muốn có thứ này từ lâu rồi.</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32286,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Bạn bè gửi lời nhắc</t>
+          <t>Bạn bè vừa nhắc nhở</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32356,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Tớ bị cấm túc trong ký túc xá (´-ι_-｀)</t>
+          <t>Ta bị cấm túc trong ký túc xá rồi (´-ι_-｀)</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32426,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Cảm ơn</t>
+          <t>Cảm ơn cậu</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32496,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Bạn bè đã offline</t>
+          <t>Bạn bè đã ngoại tuyến</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32566,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Xin cô Zahira… đ-đừng trêu chọc em như vậy…</t>
+          <t>Cô Zahira... làm ơn đừng trêu chọc tôi như thế...</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32704,7 +32706,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>(Zahira phồng má và vẽ vòng tròn trên không…)</t>
+          <t>(Zahira phồng má và vẽ vòng tròn trong không khí…)</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32776,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Lối đi bị chặn ở đây…</t>
+          <t>Con đường cụt ở đây rồi…</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32846,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Dù có "phù phép" nó cũng không được đâu…</t>
+          <t>Dùng "phép thuật" lên nó thì cũng vô ích thôi…</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32916,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>*Tiếng kêu vang tự hào*</t>
+          <t>*Tiếng kêu kiêu hãnh, vang dội*</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32986,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Mọi người đã tự tay xây dựng một mái ấm ở vùng đất băng giá Lahai-Roi…</t>
+          <t>Họ đã tự tay xây dựng tổ ấm trên vùng băng giá của Lahai-Roi…</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33056,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Chuuuluuu… chu—%#…@lu… chululu…</t>
+          <t>Chùùùù… chù—%#…@lù… chululu…</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33126,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Được rồi, đến lúc giải mã rồi—</t>
+          <t>Được rồi, đến lúc phiên dịch rồi—</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33196,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Roger, tớ đưa cậu đến đây rồi… Hmm… Có lẽ ý là thế này…</t>
+          <t>Nhận lệnh, tôi đã đưa cậu đến đây... Hmm... Chắc là chỗ này...</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33266,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>"Matthew đã dạy chúng ta ý nghĩa của Tình Bạn, và sau khi biểu diễn Bản Hòa Tấu này cùng cậu—"</t>
+          <t>"Matthew đã dạy chúng ta ý nghĩa của Tình Bạn, và sau khi cùng cậu biểu diễn bản Nhạc Khúc này—"</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33336,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>"Nhưng giờ tớ hơi lạc mất… Phần của tớ ở đâu nhỉ… âm Mi ấy…"</t>
+          <t>"Nhưng giờ ta lại quên mất... Phần của ta ở đâu nhỉ... âm thanh của Mi..."</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33406,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>"Nhưng giờ… giờ tớ không chắc nữa…"</t>
+          <t>"Nhưng giờ... giờ ta không còn chắc chắn nữa..."</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33476,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Good Luck</t>
+          <t>Chúc May Mắn</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33546,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Star Pattern 1</t>
+          <t>Hoa Văn Sao 1</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33616,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Star Pattern 2</t>
+          <t>Hoa Văn Sao 2</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33686,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Star Pattern 3</t>
+          <t>Hoa Văn Sao 3</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33756,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Star Pattern 4</t>
+          <t>Hoa Văn Sao 4</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33826,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Like</t>
+          <t>Giống như</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33896,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Với những bức ảnh này, tớ có thể làm thêm vài tấm bưu thiếp…</t>
+          <t>Với mấy tấm ảnh này, mình có thể làm thêm vài tấm bưu thiếp…</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34314,7 +34316,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Erio, Department of Voidmatters</t>
+          <t>Erio, Bộ phận Vật Chất Hư Không</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34386,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Outcast Camp Photo</t>
+          <t>Ảnh trại Kẻ bị ruồng bỏ</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34456,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Unread Messages (3)</t>
+          <t>Tin Nhắn Chưa Đọc (3)</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34526,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Yesterday 08:05</t>
+          <t>Hôm qua, 08:05</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34596,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Yesterday 11:57</t>
+          <t>11:57 hôm qua</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34666,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Yesterday 18:16</t>
+          <t>18:16 hôm qua</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34736,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Bạn có tin nhắn mới</t>
+          <t>Ngươi có tin nhắn mới</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34806,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Bạn có tin nhắn mới</t>
+          <t>Ngươi có tin nhắn mới</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34876,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Bạn có tin nhắn mới</t>
+          <t>Ngươi có tin nhắn mới</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34946,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Bạn có tin nhắn mới</t>
+          <t>Ngươi có tin nhắn mới</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35016,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Well…</t>
+          <t>Ừm…</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35086,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Bạn có tin nhắn mới</t>
+          <t>Ngươi có tin nhắn mới</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35156,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Bạn có tin nhắn mới</t>
+          <t>Ngươi có tin nhắn mới</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35226,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Bạn có tin nhắn mới</t>
+          <t>Ngươi có tin nhắn mới</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35296,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Bạn có tin nhắn mới</t>
+          <t>Ngươi có tin nhắn mới</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35366,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Bạn có tin nhắn mới</t>
+          <t>Ngươi có tin nhắn mới</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35436,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Bạn có tin nhắn mới</t>
+          <t>Ngươi có tin nhắn mới</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35506,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
